--- a/strategy/output/000063.SZ_2025-01-01_2025-09-01_comparison.xlsx
+++ b/strategy/output/000063.SZ_2025-01-01_2025-09-01_comparison.xlsx
@@ -440,12 +440,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>StrategyV1(两档买入/分批止盈/92%追踪/OCO接回)</t>
+          <t>StrategyV1(-0.7/-1.4/Breakout; TP10/20 50%; 92%Trail; OCO Rebuy)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>StrategyV2(1/3+1/3止盈/余仓追踪/止盈与止损接回)</t>
+          <t>StrategyV2(1/3@10%,1/3@20%,92%Trail; TP/SL Rebuys)</t>
         </is>
       </c>
     </row>
